--- a/ai/ai-tools/promptengineering/提示词框架.xlsx
+++ b/ai/ai-tools/promptengineering/提示词框架.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26660" windowHeight="13160" activeTab="2"/>
+    <workbookView windowWidth="26540" windowHeight="13160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="CRISPE" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="108">
   <si>
     <t>字母</t>
   </si>
@@ -289,6 +289,16 @@
 [输出]：[在此填入规定格式，如JSON/表格/Markdown]
 [限制]：[在此填入禁止事项或字数等硬性条件]
 [步骤]：[可选，填入执行逻辑，如“先分析后结论”]
+【Optimization-优化】：
+[在此填入检查维度、算法策略或评估标准，提升专业度与针对性]</t>
+  </si>
+  <si>
+    <t>【Instruction-指令】：
+[在此填入核心任务，动词精准、目标单一]
+【Context-上下文】：
+[在此填入业务场景、规范及待处理的具体数据或内容]
+【Action-约束】：
+[在此填入禁止事项、硬性条件及执行逻辑（如“先分析后结论”）]
 【Optimization-优化】：
 [在此填入检查维度、算法策略或评估标准，提升专业度与针对性]</t>
   </si>
@@ -1103,7 +1113,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1133,6 +1143,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1476,7 +1489,7 @@
       </c>
     </row>
     <row r="2" ht="17" spans="1:4">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -1490,7 +1503,7 @@
       </c>
     </row>
     <row r="3" ht="17" spans="1:4">
-      <c r="A3" s="11"/>
+      <c r="A3" s="12"/>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
       <c r="D3" s="9" t="s">
@@ -1498,7 +1511,7 @@
       </c>
     </row>
     <row r="4" ht="17" spans="1:4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -1512,7 +1525,7 @@
       </c>
     </row>
     <row r="5" ht="17" spans="1:4">
-      <c r="A5" s="11"/>
+      <c r="A5" s="12"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9" t="s">
@@ -1520,7 +1533,7 @@
       </c>
     </row>
     <row r="6" ht="17" spans="1:4">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1534,7 +1547,7 @@
       </c>
     </row>
     <row r="7" ht="17" spans="1:4">
-      <c r="A7" s="11"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9" t="s">
@@ -1542,7 +1555,7 @@
       </c>
     </row>
     <row r="8" ht="17" spans="1:4">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -1556,7 +1569,7 @@
       </c>
     </row>
     <row r="9" ht="17" spans="1:4">
-      <c r="A9" s="11"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9" t="s">
@@ -1564,7 +1577,7 @@
       </c>
     </row>
     <row r="10" ht="17" spans="1:4">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1578,7 +1591,7 @@
       </c>
     </row>
     <row r="11" ht="17" spans="1:4">
-      <c r="A11" s="11"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9" t="s">
@@ -1586,7 +1599,7 @@
       </c>
     </row>
     <row r="12" ht="17" spans="1:4">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -1600,7 +1613,7 @@
       </c>
     </row>
     <row r="13" ht="17" spans="1:4">
-      <c r="A13" s="11"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9" t="s">
@@ -1927,23 +1940,28 @@
         <v>75</v>
       </c>
     </row>
+    <row r="12" ht="185" spans="1:4">
+      <c r="D12" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
     <row r="30" spans="13:13">
-      <c r="M30" s="10"/>
+      <c r="M30" s="11"/>
     </row>
     <row r="31" spans="13:13">
-      <c r="M31" s="10"/>
+      <c r="M31" s="11"/>
     </row>
     <row r="32" spans="13:13">
-      <c r="M32" s="10"/>
+      <c r="M32" s="11"/>
     </row>
     <row r="35" spans="13:13">
-      <c r="M35" s="10"/>
+      <c r="M35" s="11"/>
     </row>
     <row r="36" spans="13:13">
-      <c r="M36" s="10"/>
+      <c r="M36" s="11"/>
     </row>
     <row r="40" spans="13:13">
-      <c r="M40" s="10"/>
+      <c r="M40" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1981,87 +1999,87 @@
   <sheetData>
     <row r="1" ht="19" customHeight="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2084,26 +2102,26 @@
   <sheetData>
     <row r="1" ht="101" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" ht="84" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
